--- a/mobile/assets/templates/gt_hybrid.xlsx
+++ b/mobile/assets/templates/gt_hybrid.xlsx
@@ -8200,8 +8200,8 @@
     <mergeCell ref="M10:N10"/>
     <mergeCell ref="F16:I16"/>
     <mergeCell ref="F25:I25"/>
+    <mergeCell ref="B8:I8"/>
     <mergeCell ref="N39:O39"/>
-    <mergeCell ref="B8:I8"/>
     <mergeCell ref="J19:M19"/>
     <mergeCell ref="P39:Q39"/>
     <mergeCell ref="J28:M28"/>
@@ -8317,7 +8317,8 @@
     <mergeCell ref="K2:Q2"/>
     <mergeCell ref="N36:O36"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.1968503937007874" right="0.1968503937007874" top="0.3543307086614173" bottom="0.3543307086614173" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" paperSize="9"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
@@ -9848,8 +9849,8 @@
     <mergeCell ref="B19:E19"/>
     <mergeCell ref="J9:L9"/>
     <mergeCell ref="B28:E28"/>
+    <mergeCell ref="W38:AJ38"/>
     <mergeCell ref="I27:I28"/>
-    <mergeCell ref="W38:AJ38"/>
     <mergeCell ref="J23:Q23"/>
     <mergeCell ref="W28:AD28"/>
     <mergeCell ref="N19:Q19"/>
@@ -9870,7 +9871,8 @@
     <mergeCell ref="W42:AJ42"/>
     <mergeCell ref="K2:Q2"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.1968503937007874" right="0.1968503937007874" top="0.3543307086614173" bottom="0.3543307086614173" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" paperSize="9"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
@@ -11209,10 +11211,10 @@
     <mergeCell ref="B53:D53"/>
     <mergeCell ref="D22:E22"/>
     <mergeCell ref="B47:Q50"/>
+    <mergeCell ref="N22:O22"/>
     <mergeCell ref="C45:P45"/>
-    <mergeCell ref="N22:O22"/>
+    <mergeCell ref="K26:L26"/>
     <mergeCell ref="B34:D34"/>
-    <mergeCell ref="K26:L26"/>
     <mergeCell ref="N36:Q36"/>
     <mergeCell ref="F53:I53"/>
     <mergeCell ref="I8:K8"/>
@@ -11304,7 +11306,8 @@
     <mergeCell ref="J52:Q52"/>
     <mergeCell ref="H26:I26"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.1968503937007874" right="0.1968503937007874" top="0.3543307086614173" bottom="0.3543307086614173" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" paperSize="9"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
@@ -22303,7 +22306,8 @@
     <mergeCell ref="H25:J25"/>
     <mergeCell ref="H26:I26"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.1968503937007874" right="0.1968503937007874" top="0.3543307086614173" bottom="0.3543307086614173" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" paperSize="9"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
@@ -24983,7 +24987,8 @@
     <mergeCell ref="O17:S17"/>
     <mergeCell ref="O11:S11"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.1968503937007874" right="0.1968503937007874" top="0.3543307086614173" bottom="0.3543307086614173" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" paperSize="9"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
@@ -26050,7 +26055,6 @@
     <mergeCell ref="J8:Q8"/>
     <mergeCell ref="B47:C47"/>
     <mergeCell ref="B16:C16"/>
-    <mergeCell ref="K18:L18"/>
     <mergeCell ref="X28:AF28"/>
     <mergeCell ref="F16:G16"/>
     <mergeCell ref="D19:E19"/>
@@ -26107,15 +26111,17 @@
     <mergeCell ref="J10:L10"/>
     <mergeCell ref="O18:Q18"/>
     <mergeCell ref="B2:F3"/>
+    <mergeCell ref="I40:J40"/>
     <mergeCell ref="H18:I18"/>
     <mergeCell ref="O38:P38"/>
     <mergeCell ref="K19:L19"/>
     <mergeCell ref="B52:D52"/>
     <mergeCell ref="G40:H40"/>
     <mergeCell ref="K2:Q2"/>
-    <mergeCell ref="I40:J40"/>
+    <mergeCell ref="K18:L18"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.1968503937007874" right="0.1968503937007874" top="0.3543307086614173" bottom="0.3543307086614173" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" paperSize="9"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
--- a/mobile/assets/templates/gt_hybrid.xlsx
+++ b/mobile/assets/templates/gt_hybrid.xlsx
@@ -8200,8 +8200,8 @@
     <mergeCell ref="M10:N10"/>
     <mergeCell ref="F16:I16"/>
     <mergeCell ref="F25:I25"/>
+    <mergeCell ref="N39:O39"/>
     <mergeCell ref="B8:I8"/>
-    <mergeCell ref="N39:O39"/>
     <mergeCell ref="J19:M19"/>
     <mergeCell ref="P39:Q39"/>
     <mergeCell ref="J28:M28"/>
@@ -9849,8 +9849,8 @@
     <mergeCell ref="B19:E19"/>
     <mergeCell ref="J9:L9"/>
     <mergeCell ref="B28:E28"/>
+    <mergeCell ref="I27:I28"/>
     <mergeCell ref="W38:AJ38"/>
-    <mergeCell ref="I27:I28"/>
     <mergeCell ref="J23:Q23"/>
     <mergeCell ref="W28:AD28"/>
     <mergeCell ref="N19:Q19"/>
@@ -11211,10 +11211,10 @@
     <mergeCell ref="B53:D53"/>
     <mergeCell ref="D22:E22"/>
     <mergeCell ref="B47:Q50"/>
+    <mergeCell ref="C45:P45"/>
     <mergeCell ref="N22:O22"/>
-    <mergeCell ref="C45:P45"/>
+    <mergeCell ref="B34:D34"/>
     <mergeCell ref="K26:L26"/>
-    <mergeCell ref="B34:D34"/>
     <mergeCell ref="N36:Q36"/>
     <mergeCell ref="F53:I53"/>
     <mergeCell ref="I8:K8"/>
@@ -26055,6 +26055,7 @@
     <mergeCell ref="J8:Q8"/>
     <mergeCell ref="B47:C47"/>
     <mergeCell ref="B16:C16"/>
+    <mergeCell ref="K18:L18"/>
     <mergeCell ref="X28:AF28"/>
     <mergeCell ref="F16:G16"/>
     <mergeCell ref="D19:E19"/>
@@ -26111,14 +26112,13 @@
     <mergeCell ref="J10:L10"/>
     <mergeCell ref="O18:Q18"/>
     <mergeCell ref="B2:F3"/>
-    <mergeCell ref="I40:J40"/>
     <mergeCell ref="H18:I18"/>
     <mergeCell ref="O38:P38"/>
     <mergeCell ref="K19:L19"/>
     <mergeCell ref="B52:D52"/>
     <mergeCell ref="G40:H40"/>
     <mergeCell ref="K2:Q2"/>
-    <mergeCell ref="K18:L18"/>
+    <mergeCell ref="I40:J40"/>
   </mergeCells>
   <pageMargins left="0.1968503937007874" right="0.1968503937007874" top="0.3543307086614173" bottom="0.3543307086614173" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9"/>

--- a/mobile/assets/templates/gt_hybrid.xlsx
+++ b/mobile/assets/templates/gt_hybrid.xlsx
@@ -3074,7 +3074,7 @@
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:t/>
+                  <a:t>None</a:t>
                 </a:r>
                 <a:endParaRPr lang="tr-TR"/>
               </a:p>
@@ -3227,7 +3227,7 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:t/>
+              <a:t>None</a:t>
             </a:r>
             <a:endParaRPr lang="tr-TR"/>
           </a:p>
@@ -3272,7 +3272,7 @@
             </a:defRPr>
           </a:pPr>
           <a:r>
-            <a:t/>
+            <a:t>None</a:t>
           </a:r>
           <a:endParaRPr lang="tr-TR"/>
         </a:p>
@@ -3512,7 +3512,7 @@
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:t/>
+                  <a:t>None</a:t>
                 </a:r>
                 <a:endParaRPr lang="tr-TR"/>
               </a:p>
@@ -3665,7 +3665,7 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:t/>
+              <a:t>None</a:t>
             </a:r>
             <a:endParaRPr lang="tr-TR"/>
           </a:p>
@@ -3710,7 +3710,7 @@
             </a:defRPr>
           </a:pPr>
           <a:r>
-            <a:t/>
+            <a:t>None</a:t>
           </a:r>
           <a:endParaRPr lang="tr-TR"/>
         </a:p>
@@ -3790,7 +3790,7 @@
             </a:defRPr>
           </a:pPr>
           <a:r>
-            <a:t/>
+            <a:t>None</a:t>
           </a:r>
           <a:endParaRPr lang="tr-TR"/>
         </a:p>
@@ -3859,7 +3859,7 @@
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:t/>
+                  <a:t>None</a:t>
                 </a:r>
                 <a:endParaRPr lang="tr-TR"/>
               </a:p>
@@ -3951,7 +3951,7 @@
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:t/>
+                  <a:t>None</a:t>
                 </a:r>
                 <a:endParaRPr lang="tr-TR"/>
               </a:p>
@@ -4069,7 +4069,7 @@
             </a:defRPr>
           </a:pPr>
           <a:r>
-            <a:t/>
+            <a:t>None</a:t>
           </a:r>
           <a:endParaRPr lang="tr-TR"/>
         </a:p>
@@ -4152,7 +4152,7 @@
             </a:defRPr>
           </a:pPr>
           <a:r>
-            <a:t/>
+            <a:t>None</a:t>
           </a:r>
           <a:endParaRPr lang="tr-TR"/>
         </a:p>
@@ -4221,7 +4221,7 @@
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:t/>
+                  <a:t>None</a:t>
                 </a:r>
                 <a:endParaRPr lang="tr-TR"/>
               </a:p>
@@ -4313,7 +4313,7 @@
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:t/>
+                  <a:t>None</a:t>
                 </a:r>
                 <a:endParaRPr lang="tr-TR"/>
               </a:p>
@@ -4431,7 +4431,7 @@
             </a:defRPr>
           </a:pPr>
           <a:r>
-            <a:t/>
+            <a:t>None</a:t>
           </a:r>
           <a:endParaRPr lang="tr-TR"/>
         </a:p>
@@ -4521,7 +4521,7 @@
             </a:defRPr>
           </a:pPr>
           <a:r>
-            <a:t/>
+            <a:t>None</a:t>
           </a:r>
           <a:endParaRPr lang="tr-TR"/>
         </a:p>
@@ -4594,7 +4594,7 @@
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:t/>
+                  <a:t>None</a:t>
                 </a:r>
                 <a:endParaRPr lang="tr-TR"/>
               </a:p>
@@ -4686,7 +4686,7 @@
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:t/>
+                  <a:t>None</a:t>
                 </a:r>
                 <a:endParaRPr lang="tr-TR"/>
               </a:p>
@@ -4804,7 +4804,7 @@
             </a:defRPr>
           </a:pPr>
           <a:r>
-            <a:t/>
+            <a:t>None</a:t>
           </a:r>
           <a:endParaRPr lang="tr-TR"/>
         </a:p>
@@ -4887,7 +4887,7 @@
             </a:defRPr>
           </a:pPr>
           <a:r>
-            <a:t/>
+            <a:t>None</a:t>
           </a:r>
           <a:endParaRPr lang="tr-TR"/>
         </a:p>
@@ -4984,7 +4984,7 @@
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:t/>
+                  <a:t>None</a:t>
                 </a:r>
                 <a:endParaRPr lang="tr-TR"/>
               </a:p>
@@ -5096,7 +5096,7 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:t/>
+              <a:t>None</a:t>
             </a:r>
             <a:endParaRPr lang="tr-TR"/>
           </a:p>
@@ -5158,7 +5158,7 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:t/>
+              <a:t>None</a:t>
             </a:r>
             <a:endParaRPr lang="tr-TR"/>
           </a:p>
@@ -5197,7 +5197,7 @@
             </a:defRPr>
           </a:pPr>
           <a:r>
-            <a:t/>
+            <a:t>None</a:t>
           </a:r>
           <a:endParaRPr lang="tr-TR"/>
         </a:p>
@@ -6687,25 +6687,11 @@
     <row r="30" s="227"/>
     <row r="31"/>
     <row r="32" ht="11.25" customHeight="1" s="227"/>
-    <row r="33"/>
-    <row r="34"/>
-    <row r="35"/>
-    <row r="36"/>
-    <row r="37"/>
-    <row r="38"/>
-    <row r="39"/>
     <row r="40" s="227"/>
     <row r="41" s="227"/>
     <row r="42" s="227"/>
-    <row r="43"/>
     <row r="44" s="227"/>
-    <row r="45"/>
-    <row r="46"/>
-    <row r="47"/>
     <row r="48" ht="7.5" customHeight="1" s="227"/>
-    <row r="49"/>
-    <row r="50"/>
-    <row r="51"/>
     <row r="52">
       <c r="A52" s="481" t="n"/>
       <c r="B52" s="99" t="n"/>
@@ -21230,7 +21216,7 @@
       </c>
       <c r="C16" s="482" t="n"/>
       <c r="D16" s="515" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E16" s="482" t="n"/>
       <c r="F16" s="516" t="inlineStr">
@@ -21487,7 +21473,7 @@
       </c>
       <c r="E26" s="99" t="n"/>
       <c r="F26" s="525" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G26" s="526" t="inlineStr">
         <is>
@@ -21544,7 +21530,7 @@
       </c>
       <c r="E27" s="99" t="n"/>
       <c r="F27" s="525" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G27" s="526" t="inlineStr">
         <is>
@@ -21601,7 +21587,7 @@
       </c>
       <c r="E28" s="99" t="n"/>
       <c r="F28" s="525" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G28" s="526" t="inlineStr">
         <is>
@@ -21658,7 +21644,7 @@
       </c>
       <c r="E29" s="99" t="n"/>
       <c r="F29" s="525" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G29" s="526" t="inlineStr">
         <is>

--- a/mobile/assets/templates/gt_hybrid.xlsx
+++ b/mobile/assets/templates/gt_hybrid.xlsx
@@ -3074,7 +3074,7 @@
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:t>None</a:t>
+                  <a:t/>
                 </a:r>
                 <a:endParaRPr lang="tr-TR"/>
               </a:p>
@@ -3227,7 +3227,7 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:t>None</a:t>
+              <a:t/>
             </a:r>
             <a:endParaRPr lang="tr-TR"/>
           </a:p>
@@ -3272,7 +3272,7 @@
             </a:defRPr>
           </a:pPr>
           <a:r>
-            <a:t>None</a:t>
+            <a:t/>
           </a:r>
           <a:endParaRPr lang="tr-TR"/>
         </a:p>
@@ -3512,7 +3512,7 @@
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:t>None</a:t>
+                  <a:t/>
                 </a:r>
                 <a:endParaRPr lang="tr-TR"/>
               </a:p>
@@ -3665,7 +3665,7 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:t>None</a:t>
+              <a:t/>
             </a:r>
             <a:endParaRPr lang="tr-TR"/>
           </a:p>
@@ -3710,7 +3710,7 @@
             </a:defRPr>
           </a:pPr>
           <a:r>
-            <a:t>None</a:t>
+            <a:t/>
           </a:r>
           <a:endParaRPr lang="tr-TR"/>
         </a:p>
@@ -3790,7 +3790,7 @@
             </a:defRPr>
           </a:pPr>
           <a:r>
-            <a:t>None</a:t>
+            <a:t/>
           </a:r>
           <a:endParaRPr lang="tr-TR"/>
         </a:p>
@@ -3859,7 +3859,7 @@
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:t>None</a:t>
+                  <a:t/>
                 </a:r>
                 <a:endParaRPr lang="tr-TR"/>
               </a:p>
@@ -3951,7 +3951,7 @@
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:t>None</a:t>
+                  <a:t/>
                 </a:r>
                 <a:endParaRPr lang="tr-TR"/>
               </a:p>
@@ -4069,7 +4069,7 @@
             </a:defRPr>
           </a:pPr>
           <a:r>
-            <a:t>None</a:t>
+            <a:t/>
           </a:r>
           <a:endParaRPr lang="tr-TR"/>
         </a:p>
@@ -4152,7 +4152,7 @@
             </a:defRPr>
           </a:pPr>
           <a:r>
-            <a:t>None</a:t>
+            <a:t/>
           </a:r>
           <a:endParaRPr lang="tr-TR"/>
         </a:p>
@@ -4221,7 +4221,7 @@
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:t>None</a:t>
+                  <a:t/>
                 </a:r>
                 <a:endParaRPr lang="tr-TR"/>
               </a:p>
@@ -4313,7 +4313,7 @@
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:t>None</a:t>
+                  <a:t/>
                 </a:r>
                 <a:endParaRPr lang="tr-TR"/>
               </a:p>
@@ -4431,7 +4431,7 @@
             </a:defRPr>
           </a:pPr>
           <a:r>
-            <a:t>None</a:t>
+            <a:t/>
           </a:r>
           <a:endParaRPr lang="tr-TR"/>
         </a:p>
@@ -4521,7 +4521,7 @@
             </a:defRPr>
           </a:pPr>
           <a:r>
-            <a:t>None</a:t>
+            <a:t/>
           </a:r>
           <a:endParaRPr lang="tr-TR"/>
         </a:p>
@@ -4594,7 +4594,7 @@
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:t>None</a:t>
+                  <a:t/>
                 </a:r>
                 <a:endParaRPr lang="tr-TR"/>
               </a:p>
@@ -4686,7 +4686,7 @@
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:t>None</a:t>
+                  <a:t/>
                 </a:r>
                 <a:endParaRPr lang="tr-TR"/>
               </a:p>
@@ -4804,7 +4804,7 @@
             </a:defRPr>
           </a:pPr>
           <a:r>
-            <a:t>None</a:t>
+            <a:t/>
           </a:r>
           <a:endParaRPr lang="tr-TR"/>
         </a:p>
@@ -4887,7 +4887,7 @@
             </a:defRPr>
           </a:pPr>
           <a:r>
-            <a:t>None</a:t>
+            <a:t/>
           </a:r>
           <a:endParaRPr lang="tr-TR"/>
         </a:p>
@@ -4984,7 +4984,7 @@
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:t>None</a:t>
+                  <a:t/>
                 </a:r>
                 <a:endParaRPr lang="tr-TR"/>
               </a:p>
@@ -5096,7 +5096,7 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:t>None</a:t>
+              <a:t/>
             </a:r>
             <a:endParaRPr lang="tr-TR"/>
           </a:p>
@@ -5158,7 +5158,7 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:t>None</a:t>
+              <a:t/>
             </a:r>
             <a:endParaRPr lang="tr-TR"/>
           </a:p>
@@ -5197,7 +5197,7 @@
             </a:defRPr>
           </a:pPr>
           <a:r>
-            <a:t>None</a:t>
+            <a:t/>
           </a:r>
           <a:endParaRPr lang="tr-TR"/>
         </a:p>
@@ -6687,11 +6687,25 @@
     <row r="30" s="227"/>
     <row r="31"/>
     <row r="32" ht="11.25" customHeight="1" s="227"/>
+    <row r="33"/>
+    <row r="34"/>
+    <row r="35"/>
+    <row r="36"/>
+    <row r="37"/>
+    <row r="38"/>
+    <row r="39"/>
     <row r="40" s="227"/>
     <row r="41" s="227"/>
     <row r="42" s="227"/>
+    <row r="43"/>
     <row r="44" s="227"/>
+    <row r="45"/>
+    <row r="46"/>
+    <row r="47"/>
     <row r="48" ht="7.5" customHeight="1" s="227"/>
+    <row r="49"/>
+    <row r="50"/>
+    <row r="51"/>
     <row r="52">
       <c r="A52" s="481" t="n"/>
       <c r="B52" s="99" t="n"/>

--- a/mobile/assets/templates/gt_hybrid.xlsx
+++ b/mobile/assets/templates/gt_hybrid.xlsx
@@ -3074,7 +3074,7 @@
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:t/>
+                  <a:t>None</a:t>
                 </a:r>
                 <a:endParaRPr lang="tr-TR"/>
               </a:p>
@@ -3227,7 +3227,7 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:t/>
+              <a:t>None</a:t>
             </a:r>
             <a:endParaRPr lang="tr-TR"/>
           </a:p>
@@ -3272,7 +3272,7 @@
             </a:defRPr>
           </a:pPr>
           <a:r>
-            <a:t/>
+            <a:t>None</a:t>
           </a:r>
           <a:endParaRPr lang="tr-TR"/>
         </a:p>
@@ -3512,7 +3512,7 @@
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:t/>
+                  <a:t>None</a:t>
                 </a:r>
                 <a:endParaRPr lang="tr-TR"/>
               </a:p>
@@ -3665,7 +3665,7 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:t/>
+              <a:t>None</a:t>
             </a:r>
             <a:endParaRPr lang="tr-TR"/>
           </a:p>
@@ -3710,7 +3710,7 @@
             </a:defRPr>
           </a:pPr>
           <a:r>
-            <a:t/>
+            <a:t>None</a:t>
           </a:r>
           <a:endParaRPr lang="tr-TR"/>
         </a:p>
@@ -3790,7 +3790,7 @@
             </a:defRPr>
           </a:pPr>
           <a:r>
-            <a:t/>
+            <a:t>None</a:t>
           </a:r>
           <a:endParaRPr lang="tr-TR"/>
         </a:p>
@@ -3859,7 +3859,7 @@
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:t/>
+                  <a:t>None</a:t>
                 </a:r>
                 <a:endParaRPr lang="tr-TR"/>
               </a:p>
@@ -3951,7 +3951,7 @@
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:t/>
+                  <a:t>None</a:t>
                 </a:r>
                 <a:endParaRPr lang="tr-TR"/>
               </a:p>
@@ -4069,7 +4069,7 @@
             </a:defRPr>
           </a:pPr>
           <a:r>
-            <a:t/>
+            <a:t>None</a:t>
           </a:r>
           <a:endParaRPr lang="tr-TR"/>
         </a:p>
@@ -4152,7 +4152,7 @@
             </a:defRPr>
           </a:pPr>
           <a:r>
-            <a:t/>
+            <a:t>None</a:t>
           </a:r>
           <a:endParaRPr lang="tr-TR"/>
         </a:p>
@@ -4221,7 +4221,7 @@
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:t/>
+                  <a:t>None</a:t>
                 </a:r>
                 <a:endParaRPr lang="tr-TR"/>
               </a:p>
@@ -4313,7 +4313,7 @@
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:t/>
+                  <a:t>None</a:t>
                 </a:r>
                 <a:endParaRPr lang="tr-TR"/>
               </a:p>
@@ -4431,7 +4431,7 @@
             </a:defRPr>
           </a:pPr>
           <a:r>
-            <a:t/>
+            <a:t>None</a:t>
           </a:r>
           <a:endParaRPr lang="tr-TR"/>
         </a:p>
@@ -4521,7 +4521,7 @@
             </a:defRPr>
           </a:pPr>
           <a:r>
-            <a:t/>
+            <a:t>None</a:t>
           </a:r>
           <a:endParaRPr lang="tr-TR"/>
         </a:p>
@@ -4594,7 +4594,7 @@
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:t/>
+                  <a:t>None</a:t>
                 </a:r>
                 <a:endParaRPr lang="tr-TR"/>
               </a:p>
@@ -4686,7 +4686,7 @@
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:t/>
+                  <a:t>None</a:t>
                 </a:r>
                 <a:endParaRPr lang="tr-TR"/>
               </a:p>
@@ -4804,7 +4804,7 @@
             </a:defRPr>
           </a:pPr>
           <a:r>
-            <a:t/>
+            <a:t>None</a:t>
           </a:r>
           <a:endParaRPr lang="tr-TR"/>
         </a:p>
@@ -4887,7 +4887,7 @@
             </a:defRPr>
           </a:pPr>
           <a:r>
-            <a:t/>
+            <a:t>None</a:t>
           </a:r>
           <a:endParaRPr lang="tr-TR"/>
         </a:p>
@@ -4984,7 +4984,7 @@
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:t/>
+                  <a:t>None</a:t>
                 </a:r>
                 <a:endParaRPr lang="tr-TR"/>
               </a:p>
@@ -5096,7 +5096,7 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:t/>
+              <a:t>None</a:t>
             </a:r>
             <a:endParaRPr lang="tr-TR"/>
           </a:p>
@@ -5158,7 +5158,7 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:t/>
+              <a:t>None</a:t>
             </a:r>
             <a:endParaRPr lang="tr-TR"/>
           </a:p>
@@ -5197,7 +5197,7 @@
             </a:defRPr>
           </a:pPr>
           <a:r>
-            <a:t/>
+            <a:t>None</a:t>
           </a:r>
           <a:endParaRPr lang="tr-TR"/>
         </a:p>
@@ -6687,25 +6687,11 @@
     <row r="30" s="227"/>
     <row r="31"/>
     <row r="32" ht="11.25" customHeight="1" s="227"/>
-    <row r="33"/>
-    <row r="34"/>
-    <row r="35"/>
-    <row r="36"/>
-    <row r="37"/>
-    <row r="38"/>
-    <row r="39"/>
     <row r="40" s="227"/>
     <row r="41" s="227"/>
     <row r="42" s="227"/>
-    <row r="43"/>
     <row r="44" s="227"/>
-    <row r="45"/>
-    <row r="46"/>
-    <row r="47"/>
     <row r="48" ht="7.5" customHeight="1" s="227"/>
-    <row r="49"/>
-    <row r="50"/>
-    <row r="51"/>
     <row r="52">
       <c r="A52" s="481" t="n"/>
       <c r="B52" s="99" t="n"/>
@@ -13236,29 +13222,10 @@
     <row r="43" ht="3" customHeight="1" s="227">
       <c r="A43" s="10" t="n"/>
       <c r="B43" s="485" t="n"/>
-      <c r="C43" s="47" t="n"/>
-      <c r="D43" s="47" t="n"/>
-      <c r="E43" s="47" t="n"/>
-      <c r="F43" s="47" t="n"/>
-      <c r="G43" s="47" t="n"/>
-      <c r="H43" s="47" t="n"/>
-      <c r="I43" s="47" t="n"/>
-      <c r="J43" s="47" t="n"/>
-      <c r="K43" s="47" t="n"/>
-      <c r="L43" s="47" t="n"/>
-      <c r="M43" s="47" t="n"/>
-      <c r="N43" s="47" t="n"/>
-      <c r="O43" s="47" t="n"/>
-      <c r="P43" s="47" t="n"/>
-      <c r="Q43" s="47" t="n"/>
-      <c r="R43" s="47" t="n"/>
-      <c r="S43" s="211" t="n"/>
       <c r="T43" s="11" t="n"/>
     </row>
     <row r="44" ht="15.75" customHeight="1" s="227">
       <c r="A44" s="10" t="n"/>
-      <c r="B44" s="62" t="n"/>
-      <c r="S44" s="212" t="n"/>
       <c r="T44" s="11" t="n"/>
       <c r="V44" s="485" t="inlineStr">
         <is>
@@ -13289,8 +13256,6 @@
     </row>
     <row r="45" ht="3" customHeight="1" s="227">
       <c r="A45" s="10" t="n"/>
-      <c r="B45" s="62" t="n"/>
-      <c r="S45" s="212" t="n"/>
       <c r="T45" s="11" t="n"/>
       <c r="V45" s="3" t="n"/>
       <c r="W45" s="127" t="n"/>
@@ -13313,8 +13278,6 @@
     </row>
     <row r="46">
       <c r="A46" s="10" t="n"/>
-      <c r="B46" s="62" t="n"/>
-      <c r="S46" s="212" t="n"/>
       <c r="T46" s="11" t="n"/>
       <c r="V46" s="489" t="inlineStr">
         <is>
@@ -13361,8 +13324,6 @@
     </row>
     <row r="47" ht="3" customHeight="1" s="227">
       <c r="A47" s="10" t="n"/>
-      <c r="B47" s="62" t="n"/>
-      <c r="S47" s="212" t="n"/>
       <c r="T47" s="11" t="n"/>
       <c r="V47" s="3" t="n"/>
       <c r="W47" s="127" t="n"/>
@@ -13385,8 +13346,6 @@
     </row>
     <row r="48">
       <c r="A48" s="10" t="n"/>
-      <c r="B48" s="62" t="n"/>
-      <c r="S48" s="212" t="n"/>
       <c r="T48" s="11" t="n"/>
       <c r="V48" s="490">
         <f>V57/1.0525889</f>
@@ -13427,8 +13386,6 @@
     </row>
     <row r="49" ht="3" customHeight="1" s="227">
       <c r="A49" s="10" t="n"/>
-      <c r="B49" s="62" t="n"/>
-      <c r="S49" s="212" t="n"/>
       <c r="T49" s="11" t="n"/>
       <c r="V49" s="42" t="n"/>
       <c r="W49" s="43" t="n"/>
@@ -13451,8 +13408,6 @@
     </row>
     <row r="50">
       <c r="A50" s="10" t="n"/>
-      <c r="B50" s="62" t="n"/>
-      <c r="S50" s="212" t="n"/>
       <c r="T50" s="11" t="n"/>
       <c r="V50" s="328" t="inlineStr">
         <is>
@@ -13499,24 +13454,6 @@
     </row>
     <row r="51" ht="3" customHeight="1" s="227">
       <c r="A51" s="10" t="n"/>
-      <c r="B51" s="49" t="n"/>
-      <c r="C51" s="50" t="n"/>
-      <c r="D51" s="50" t="n"/>
-      <c r="E51" s="50" t="n"/>
-      <c r="F51" s="50" t="n"/>
-      <c r="G51" s="50" t="n"/>
-      <c r="H51" s="50" t="n"/>
-      <c r="I51" s="50" t="n"/>
-      <c r="J51" s="50" t="n"/>
-      <c r="K51" s="50" t="n"/>
-      <c r="L51" s="50" t="n"/>
-      <c r="M51" s="50" t="n"/>
-      <c r="N51" s="50" t="n"/>
-      <c r="O51" s="50" t="n"/>
-      <c r="P51" s="50" t="n"/>
-      <c r="Q51" s="50" t="n"/>
-      <c r="R51" s="50" t="n"/>
-      <c r="S51" s="213" t="n"/>
       <c r="T51" s="11" t="n"/>
     </row>
     <row r="52" ht="3" customHeight="1" s="227">
@@ -14751,7 +14688,7 @@
       <c r="T83" s="17" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="161">
+  <mergeCells count="160">
     <mergeCell ref="G55:J55"/>
     <mergeCell ref="F68:G68"/>
     <mergeCell ref="AL57:AN57"/>
@@ -14763,7 +14700,6 @@
     <mergeCell ref="L68:M68"/>
     <mergeCell ref="K5:S6"/>
     <mergeCell ref="V66:X66"/>
-    <mergeCell ref="B43:S51"/>
     <mergeCell ref="K17:M17"/>
     <mergeCell ref="I66:J66"/>
     <mergeCell ref="K33:N33"/>
